--- a/data/gravel/Rondo Bogan (Hi) 2025.xlsx
+++ b/data/gravel/Rondo Bogan (Hi) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D53FA1C-AC48-7549-ADF8-601EE0211836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBC559F-27F1-1C4A-80E8-A72D599193B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="520" yWindow="2200" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1460" yWindow="3020" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>a8:f31</t>
+  </si>
+  <si>
+    <t>https://rondo.cc/images/galerie/339-2635.jpg</t>
   </si>
 </sst>
 </file>
@@ -779,6 +782,11 @@
         <v>103</v>
       </c>
     </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>107</v>
+      </c>
+    </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Rondo Bogan (Hi) 2025.xlsx
+++ b/data/gravel/Rondo Bogan (Hi) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBC559F-27F1-1C4A-80E8-A72D599193B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BDE4C9-F373-7A4D-A37A-64192E5B6493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="3020" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -359,9 +359,6 @@
     <t>https://rondo.cc/bogan-st1,470,pl</t>
   </si>
   <si>
-    <t>46/30</t>
-  </si>
-  <si>
     <t>Bogan (Hi)</t>
   </si>
   <si>
@@ -369,6 +366,12 @@
   </si>
   <si>
     <t>https://rondo.cc/images/galerie/339-2635.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Gdańsk, Poland</t>
   </si>
 </sst>
 </file>
@@ -736,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z71"/>
+  <dimension ref="A1:Z72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -755,7 +758,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
@@ -784,7 +787,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
@@ -792,7 +795,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
@@ -1885,8 +1888,8 @@
       <c r="A53" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>104</v>
+      <c r="B53" s="1">
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -2003,6 +2006,14 @@
         <v>67</v>
       </c>
       <c r="B71" s="1"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>107</v>
+      </c>
+      <c r="B72" t="s">
+        <v>108</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/gravel/Rondo Bogan (Hi) 2025.xlsx
+++ b/data/gravel/Rondo Bogan (Hi) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BDE4C9-F373-7A4D-A37A-64192E5B6493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579FB5C7-9C8F-4849-B784-632B5F98A1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="3020" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1678,20 +1678,16 @@
         <v>28</v>
       </c>
       <c r="C30">
-        <f>C32</f>
         <v>165</v>
       </c>
       <c r="D30">
-        <f>AVERAGE(D32,C33)</f>
-        <v>172.5</v>
+        <v>172</v>
       </c>
       <c r="E30">
-        <f t="shared" ref="E30:F30" si="2">AVERAGE(E32,D33)</f>
-        <v>179.5</v>
+        <v>179</v>
       </c>
       <c r="F30">
-        <f t="shared" si="2"/>
-        <v>186.5</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.3">
@@ -1702,57 +1698,27 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <f>D30</f>
-        <v>172.5</v>
+        <v>173</v>
       </c>
       <c r="D31">
-        <f t="shared" ref="D31:F31" si="3">E30</f>
-        <v>179.5</v>
+        <v>180</v>
       </c>
       <c r="E31">
-        <f t="shared" si="3"/>
-        <v>186.5</v>
+        <v>187</v>
       </c>
       <c r="F31">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="C32">
-        <v>165</v>
-      </c>
-      <c r="D32">
-        <v>172</v>
-      </c>
-      <c r="E32">
-        <v>179</v>
-      </c>
-      <c r="F32">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>32</v>
       </c>
-      <c r="C33">
-        <v>173</v>
-      </c>
-      <c r="D33">
-        <v>180</v>
-      </c>
-      <c r="E33">
-        <v>187</v>
-      </c>
-      <c r="F33">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -1760,7 +1726,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>70</v>
       </c>
@@ -1768,7 +1734,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -1776,7 +1742,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -1784,7 +1750,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>34</v>
       </c>
@@ -1792,12 +1758,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>36</v>
       </c>
@@ -1806,32 +1772,32 @@
         <v>53.339999999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>42</v>
       </c>
@@ -1839,7 +1805,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -1847,7 +1813,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>44</v>
       </c>

--- a/data/gravel/Rondo Bogan (Hi) 2025.xlsx
+++ b/data/gravel/Rondo Bogan (Hi) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579FB5C7-9C8F-4849-B784-632B5F98A1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF3013D-96B4-A442-847A-37EA0EF29354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="3020" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,24 @@
   </si>
   <si>
     <t>Gdańsk, Poland</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -739,7 +757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z72"/>
+  <dimension ref="A1:Z78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1815,169 +1833,199 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50">
-        <v>27.2</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52">
-        <v>42</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53" s="1">
-        <v>46</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>50</v>
-      </c>
-      <c r="B54">
-        <v>160</v>
+        <v>44</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>51</v>
-      </c>
-      <c r="B55">
-        <v>160</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B56">
+        <v>27.2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>76</v>
+        <v>48</v>
+      </c>
+      <c r="B58">
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="B60">
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>74</v>
+        <v>57</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>67</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>107</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>108</v>
       </c>
     </row>

--- a/data/gravel/Rondo Bogan (Hi) 2025.xlsx
+++ b/data/gravel/Rondo Bogan (Hi) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF3013D-96B4-A442-847A-37EA0EF29354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B884B22-431C-FD44-B735-14C7A28FFF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="3020" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -284,21 +284,6 @@
     <t>XL</t>
   </si>
   <si>
-    <r>
-      <t>front</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Futura"/>
-        <family val="2"/>
-      </rPr>
-      <t>_center</t>
-    </r>
-  </si>
-  <si>
     <t>steel</t>
   </si>
   <si>
@@ -390,13 +375,16 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>front_center</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -418,13 +406,6 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Futura"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -460,7 +441,7 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -776,7 +757,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
@@ -800,12 +781,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
@@ -813,7 +794,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
@@ -821,7 +802,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>79</v>
@@ -842,7 +823,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="4">
         <v>409</v>
@@ -859,52 +840,52 @@
       <c r="G9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="N9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="O9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="Q9" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q9" s="3" t="s">
+      <c r="R9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="S9" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="T9" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T9" s="3" t="s">
+      <c r="U9" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="U9" s="3" t="s">
+      <c r="V9" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="V9" s="3" t="s">
+      <c r="W9" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="W9" s="3" t="s">
+      <c r="X9" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="X9" s="3" t="s">
+      <c r="Y9" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="Y9" s="3" t="s">
+      <c r="Z9" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
@@ -912,7 +893,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C10" s="4">
         <v>577</v>
@@ -928,7 +909,7 @@
       </c>
       <c r="G10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>79</v>
@@ -981,10 +962,10 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" s="4">
         <v>644</v>
@@ -1053,7 +1034,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" s="4">
         <v>573</v>
@@ -1122,7 +1103,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C13" s="4">
         <v>140</v>
@@ -1191,7 +1172,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" s="4">
         <v>470</v>
@@ -1207,7 +1188,7 @@
       </c>
       <c r="G14" s="4"/>
       <c r="J14" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>79</v>
@@ -1263,7 +1244,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="4">
         <v>435</v>
@@ -1332,7 +1313,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="4">
         <v>86</v>
@@ -1401,7 +1382,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="4">
         <v>70.8</v>
@@ -1470,7 +1451,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C18" s="4">
         <v>73.8</v>
@@ -1504,7 +1485,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C19" s="4">
         <v>390</v>
@@ -1525,7 +1506,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" s="4">
         <v>55</v>
@@ -1546,7 +1527,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C21" s="4">
         <v>170</v>
@@ -1567,7 +1548,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C22" s="4">
         <v>440</v>
@@ -1587,7 +1568,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C23" s="4">
         <v>60</v>
@@ -1765,7 +1746,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1833,32 +1814,32 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -2023,10 +2004,10 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>106</v>
+      </c>
+      <c r="B78" t="s">
         <v>107</v>
-      </c>
-      <c r="B78" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
